--- a/Day 18/Capstone Details/project_allocation.xlsx
+++ b/Day 18/Capstone Details/project_allocation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeetu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeetu\Documents\GitHub\WiproDC-25SUB5874\Day 18\Capstone Details\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB5847C-58D8-4883-8AAC-7F8574A26DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2019E82B-1914-4BE8-857E-1477CD32DAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="30">
   <si>
     <t>Participant Name</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>Mallela Aasritha</t>
+  </si>
+  <si>
+    <t>Mokshitha</t>
   </si>
 </sst>
 </file>
@@ -479,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.125" bestFit="1" customWidth="1"/>
@@ -766,6 +769,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
